--- a/public/templates/fee-upload-template.xlsx
+++ b/public/templates/fee-upload-template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -503,88 +503,292 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Tuition</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tuition (Nursery)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>cash</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>INV-001</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TUI-001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Term I fees</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Per term</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuition (Primary)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>450000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TUI-002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tuition (O-Level)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>550000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TUI-003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tuition (A-Level)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>650000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TUI-004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lunch Fee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LUN-001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRP-001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Library Fee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LIB-001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Sports Fee</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>mobile_money</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>MTN-REF-123</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SPT-001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Development Fee</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>bank_transfer</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>TRF-2026-001</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ICT Fee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ICT-001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Per term</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
